--- a/ILCA/履歴書.xlsx
+++ b/ILCA/履歴書.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KOUDAI_ISISISISISIISISSIMORI\就活\ILCA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KOUDAI\就活\KOUDAI_SHUKATU\ILCA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BC502C-6CF2-435A-9A42-8D8159E22E77}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79064B5-374D-46C6-805A-B2FE9230E204}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="13830" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -172,41 +172,7 @@
     <t>以上</t>
   </si>
   <si>
-    <t>　専門学校での共同制作では、ディレクターからの「世界観を高めたい」という</t>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
-    <t>　私の強みは、高いクオリティを目指す「チャレンジ精神」です。自発的に</t>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
-    <t>アイデアを提案し、チームの意見を取り入れながら形にすることを得意としています。</t>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
     <t>カワスイ 川崎水族館     退社</t>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
-    <t>相談に対し、イージングを活用したカメラ演出やUIアニメーションなど、一から</t>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
-    <t>提案・実装しました。さらに進捗が滞った際には自ら意見交換の場を作ることで、</t>
-    <rPh sb="31" eb="32">
-      <t>ツク</t>
-    </rPh>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
-    <t>　その結果、学内の企業様主催コンテストで最優秀賞を受賞いたしました。</t>
-    <phoneticPr fontId="16"/>
-  </si>
-  <si>
-    <t>ゲームのクオリティが向上し、作品としての面白さをより高めることができました。</t>
-    <rPh sb="10" eb="12">
-      <t>コウジョウゼンタイ</t>
-    </rPh>
     <phoneticPr fontId="16"/>
   </si>
   <si>
@@ -314,6 +280,88 @@
   </si>
   <si>
     <t>2006年　8月　15日生　(満　20　歳)</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>チームで作成したゲームが学内の企業様主催コンテストで最優秀賞を受賞いたしました。</t>
+    <rPh sb="4" eb="6">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>提案し、チームの意見を取り入れながら形にすることを得意としています。</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>　私の強みは、高いクオリティを目指す「チャレンジ精神」です。自発的にアイデアを</t>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>　共同制作の際にディレクターから、和風な雰囲気と、ポップな世界観を高めたいと</t>
+    <rPh sb="1" eb="5">
+      <t>キョウドウセイサク</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ワフウ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>フンイキ</t>
+    </rPh>
+    <rPh sb="29" eb="32">
+      <t>セカイカン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>相談を受けました。そこで、ふすまの画像を使った画面遷移やカメラ演出にイージングの</t>
+    <rPh sb="0" eb="2">
+      <t>ソウダン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ガメンセンイ</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>ブラッシュアップをすることで、クオリティの向上に貢献しました。その結果、</t>
+    <rPh sb="21" eb="23">
+      <t>コウジョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>コウケン</t>
+    </rPh>
+    <phoneticPr fontId="16"/>
+  </si>
+  <si>
+    <t>動きを導入するなどの提案・実装を行いました。チーム内で意見交換を重ねて</t>
+    <rPh sb="0" eb="1">
+      <t>ウゴ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ドウニュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>オコナ</t>
+    </rPh>
     <phoneticPr fontId="16"/>
   </si>
 </sst>
@@ -1643,6 +1691,180 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1652,6 +1874,189 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1661,370 +2066,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2620,13 +2668,13 @@
   <sheetData>
     <row r="1" spans="1:27" ht="27" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="72">
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="93">
         <v>46274</v>
       </c>
       <c r="G1" s="2"/>
@@ -2653,28 +2701,28 @@
     </row>
     <row r="2" spans="1:27" ht="19.5" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
       <c r="G2" s="2"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
-      <c r="L2" s="73" t="s">
+      <c r="L2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="74" t="s">
+      <c r="M2" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="37"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="42"/>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
@@ -2688,22 +2736,22 @@
     </row>
     <row r="3" spans="1:27" ht="3.75" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="34"/>
+      <c r="L3" s="69"/>
+      <c r="M3" s="86"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="32"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -2717,23 +2765,23 @@
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1">
       <c r="A4" s="1"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="77" t="s">
+      <c r="H4" s="97" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-      <c r="L4" s="78"/>
-      <c r="M4" s="104"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="32"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="85"/>
+      <c r="N4" s="87"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="26"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
@@ -2747,28 +2795,28 @@
     </row>
     <row r="5" spans="1:27" ht="9.75" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="84" t="s">
+      <c r="B5" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="85"/>
-      <c r="D5" s="88" t="s">
+      <c r="C5" s="103"/>
+      <c r="D5" s="104" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="90" t="s">
+      <c r="E5" s="41"/>
+      <c r="F5" s="105" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="1"/>
-      <c r="H5" s="70"/>
+      <c r="H5" s="28"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="34"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="86"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="32"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
@@ -2782,24 +2830,24 @@
     </row>
     <row r="6" spans="1:27" ht="12.75" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="89"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="91"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="106"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="92" t="s">
+      <c r="H6" s="107" t="s">
         <v>8</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="104"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="32"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="87"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="26"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
@@ -2813,28 +2861,28 @@
     </row>
     <row r="7" spans="1:27" ht="12.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="93" t="s">
+      <c r="B7" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="95" t="s">
+      <c r="C7" s="109"/>
+      <c r="D7" s="112" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="96" t="s">
+      <c r="E7" s="46"/>
+      <c r="F7" s="113" t="s">
         <v>11</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="70"/>
+      <c r="H7" s="28"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="34"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="86"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="32"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -2848,22 +2896,22 @@
     </row>
     <row r="8" spans="1:27" ht="25.5" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="46"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="89"/>
-      <c r="E8" s="70"/>
-      <c r="F8" s="97"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="114"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="70"/>
+      <c r="H8" s="28"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="3"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="18"/>
+      <c r="N8" s="88"/>
+      <c r="O8" s="75"/>
+      <c r="P8" s="75"/>
+      <c r="Q8" s="76"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
@@ -2877,22 +2925,22 @@
     </row>
     <row r="9" spans="1:27" ht="25.5" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="98"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="115"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="70"/>
+      <c r="H9" s="28"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="5"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="105"/>
-      <c r="O9" s="64"/>
-      <c r="P9" s="64"/>
-      <c r="Q9" s="65"/>
+      <c r="N9" s="89"/>
+      <c r="O9" s="90"/>
+      <c r="P9" s="90"/>
+      <c r="Q9" s="91"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -2906,13 +2954,13 @@
     </row>
     <row r="10" spans="1:27" ht="10.5" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="114" t="s">
-        <v>68</v>
+      <c r="B10" s="24" t="s">
+        <v>61</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="26"/>
       <c r="G10" s="1"/>
       <c r="H10" s="7"/>
       <c r="I10" s="1"/>
@@ -2937,26 +2985,26 @@
     </row>
     <row r="11" spans="1:27" ht="18" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="115"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="29"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-      <c r="L11" s="79" t="s">
+      <c r="L11" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="80"/>
-      <c r="N11" s="82" t="s">
+      <c r="M11" s="100"/>
+      <c r="N11" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="37"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="41"/>
+      <c r="Q11" s="42"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -2970,22 +3018,22 @@
     </row>
     <row r="12" spans="1:27" ht="8.25" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="34"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="32"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="81"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="34"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="32"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
@@ -2999,32 +3047,32 @@
     </row>
     <row r="13" spans="1:27" ht="16.5" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="100" t="s">
+      <c r="B13" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="116" t="s">
+      <c r="C13" s="34"/>
+      <c r="D13" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="119" t="s">
+      <c r="E13" s="25"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="36"/>
-      <c r="I13" s="37"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="42"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-      <c r="L13" s="134" t="s">
+      <c r="L13" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="M13" s="122"/>
-      <c r="N13" s="135" t="s">
+      <c r="M13" s="49"/>
+      <c r="N13" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="32"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="26"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
@@ -3038,22 +3086,22 @@
     </row>
     <row r="14" spans="1:27" ht="3" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="87"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="87"/>
-      <c r="G14" s="120"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="121"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="44"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="122"/>
-      <c r="N14" s="136"/>
-      <c r="O14" s="70"/>
-      <c r="P14" s="70"/>
-      <c r="Q14" s="115"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="49"/>
+      <c r="N14" s="79"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="29"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
@@ -3067,28 +3115,28 @@
     </row>
     <row r="15" spans="1:27" ht="12" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="123" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="137" t="s">
-        <v>67</v>
+      <c r="C15" s="110"/>
+      <c r="D15" s="45" t="s">
+        <v>60</v>
       </c>
-      <c r="E15" s="53"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="60" t="s">
+      <c r="E15" s="46"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="53"/>
-      <c r="I15" s="61"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="53"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="122"/>
-      <c r="N15" s="83"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="34"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="32"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -3102,26 +3150,26 @@
     </row>
     <row r="16" spans="1:27" ht="27.75" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="46"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="70"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="123" t="s">
+      <c r="B16" s="27"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="70"/>
-      <c r="I16" s="115"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="99" t="s">
+      <c r="L16" s="30"/>
+      <c r="M16" s="51"/>
+      <c r="N16" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="18"/>
+      <c r="O16" s="75"/>
+      <c r="P16" s="75"/>
+      <c r="Q16" s="76"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -3135,26 +3183,26 @@
     </row>
     <row r="17" spans="1:27" ht="11.25" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="34"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="110"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="32"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-      <c r="L17" s="100" t="s">
+      <c r="L17" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="M17" s="101"/>
-      <c r="N17" s="102" t="s">
-        <v>64</v>
+      <c r="M17" s="63"/>
+      <c r="N17" s="81" t="s">
+        <v>57</v>
       </c>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="32"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="26"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
@@ -3168,24 +3216,24 @@
     </row>
     <row r="18" spans="1:27" ht="17.25" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="47" t="s">
+      <c r="B18" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="48"/>
-      <c r="D18" s="124"/>
-      <c r="E18" s="125"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="126"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="127"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="60"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-      <c r="L18" s="49"/>
-      <c r="M18" s="55"/>
-      <c r="N18" s="103"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="42"/>
+      <c r="L18" s="64"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="83"/>
+      <c r="Q18" s="84"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
@@ -3199,20 +3247,20 @@
     </row>
     <row r="19" spans="1:27" ht="10.5" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="138" t="s">
+      <c r="C19" s="110"/>
+      <c r="D19" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="139"/>
-      <c r="F19" s="140"/>
-      <c r="G19" s="60" t="s">
+      <c r="E19" s="130"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="H19" s="53"/>
-      <c r="I19" s="61"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="53"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="7"/>
@@ -3234,28 +3282,28 @@
     </row>
     <row r="20" spans="1:27" ht="32.25" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="141"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="143"/>
-      <c r="G20" s="62" t="s">
+      <c r="B20" s="64"/>
+      <c r="C20" s="125"/>
+      <c r="D20" s="132"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="134"/>
+      <c r="G20" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="H20" s="41"/>
-      <c r="I20" s="42"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="84"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="106" t="s">
+      <c r="L20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="M20" s="107"/>
-      <c r="N20" s="108" t="s">
-        <v>63</v>
+      <c r="M20" s="17"/>
+      <c r="N20" s="18" t="s">
+        <v>56</v>
       </c>
-      <c r="O20" s="109"/>
-      <c r="P20" s="109"/>
-      <c r="Q20" s="110"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="20"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
@@ -3279,12 +3327,12 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
-      <c r="L21" s="132"/>
-      <c r="M21" s="70"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="70"/>
-      <c r="P21" s="70"/>
-      <c r="Q21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="28"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
@@ -3308,14 +3356,14 @@
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
-      <c r="L22" s="133" t="s">
+      <c r="L22" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="M22" s="57"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="57"/>
-      <c r="P22" s="57"/>
-      <c r="Q22" s="58"/>
+      <c r="M22" s="72"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="72"/>
+      <c r="P22" s="72"/>
+      <c r="Q22" s="73"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
@@ -3332,27 +3380,27 @@
       <c r="B23" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="56" t="s">
+      <c r="D23" s="127"/>
+      <c r="E23" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="58"/>
+      <c r="F23" s="72"/>
+      <c r="G23" s="72"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
-      <c r="L23" s="16" t="s">
-        <v>65</v>
+      <c r="L23" s="74" t="s">
+        <v>58</v>
       </c>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="18"/>
+      <c r="M23" s="75"/>
+      <c r="N23" s="75"/>
+      <c r="O23" s="75"/>
+      <c r="P23" s="75"/>
+      <c r="Q23" s="76"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
@@ -3367,25 +3415,25 @@
     <row r="24" spans="1:27" ht="24" customHeight="1">
       <c r="A24" s="1"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="59" t="s">
+      <c r="C24" s="117"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="136" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="18"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="75"/>
+      <c r="H24" s="75"/>
+      <c r="I24" s="76"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
-      <c r="L24" s="16" t="s">
-        <v>66</v>
+      <c r="L24" s="74" t="s">
+        <v>59</v>
       </c>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
-      <c r="P24" s="17"/>
-      <c r="Q24" s="18"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="75"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="76"/>
       <c r="R24" s="1"/>
       <c r="S24" s="10"/>
       <c r="T24" s="1"/>
@@ -3402,27 +3450,27 @@
       <c r="B25" s="11">
         <v>2022</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="128">
         <v>3</v>
       </c>
-      <c r="D25" s="29"/>
-      <c r="E25" s="38" t="s">
-        <v>60</v>
+      <c r="D25" s="118"/>
+      <c r="E25" s="88" t="s">
+        <v>53</v>
       </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="18"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="76"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
-      <c r="L25" s="19" t="s">
-        <v>49</v>
+      <c r="L25" s="138" t="s">
+        <v>64</v>
       </c>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
-      <c r="P25" s="17"/>
-      <c r="Q25" s="18"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="76"/>
       <c r="R25" s="1"/>
       <c r="S25" s="10"/>
       <c r="T25" s="1"/>
@@ -3439,27 +3487,27 @@
       <c r="B26" s="11">
         <v>2022</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="128">
         <v>4</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="28" t="s">
-        <v>61</v>
+      <c r="D26" s="118"/>
+      <c r="E26" s="117" t="s">
+        <v>54</v>
       </c>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="18"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="76"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
-      <c r="L26" s="19" t="s">
-        <v>50</v>
+      <c r="L26" s="138" t="s">
+        <v>63</v>
       </c>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="18"/>
+      <c r="M26" s="75"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="75"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="76"/>
       <c r="R26" s="1"/>
       <c r="S26" s="10"/>
       <c r="T26" s="1"/>
@@ -3476,27 +3524,27 @@
       <c r="B27" s="11">
         <v>2023</v>
       </c>
-      <c r="C27" s="43">
+      <c r="C27" s="128">
         <v>11</v>
       </c>
-      <c r="D27" s="29"/>
-      <c r="E27" s="28" t="s">
-        <v>62</v>
+      <c r="D27" s="118"/>
+      <c r="E27" s="117" t="s">
+        <v>55</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="18"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="75"/>
+      <c r="H27" s="75"/>
+      <c r="I27" s="76"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
-      <c r="L27" s="19" t="s">
-        <v>48</v>
+      <c r="L27" s="138" t="s">
+        <v>65</v>
       </c>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
-      <c r="P27" s="17"/>
-      <c r="Q27" s="18"/>
+      <c r="M27" s="75"/>
+      <c r="N27" s="75"/>
+      <c r="O27" s="75"/>
+      <c r="P27" s="75"/>
+      <c r="Q27" s="76"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
@@ -3513,27 +3561,27 @@
       <c r="B28" s="11">
         <v>2025</v>
       </c>
-      <c r="C28" s="43">
+      <c r="C28" s="128">
         <v>3</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="28" t="s">
-        <v>57</v>
+      <c r="D28" s="118"/>
+      <c r="E28" s="117" t="s">
+        <v>50</v>
       </c>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="18"/>
+      <c r="F28" s="75"/>
+      <c r="G28" s="75"/>
+      <c r="H28" s="75"/>
+      <c r="I28" s="76"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
-      <c r="L28" s="19" t="s">
-        <v>52</v>
+      <c r="L28" s="138" t="s">
+        <v>66</v>
       </c>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-      <c r="P28" s="17"/>
-      <c r="Q28" s="18"/>
+      <c r="M28" s="75"/>
+      <c r="N28" s="75"/>
+      <c r="O28" s="75"/>
+      <c r="P28" s="75"/>
+      <c r="Q28" s="76"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
@@ -3550,27 +3598,27 @@
       <c r="B29" s="11">
         <v>2025</v>
       </c>
-      <c r="C29" s="43">
+      <c r="C29" s="128">
         <v>4</v>
       </c>
-      <c r="D29" s="29"/>
-      <c r="E29" s="28" t="s">
-        <v>58</v>
+      <c r="D29" s="118"/>
+      <c r="E29" s="117" t="s">
+        <v>51</v>
       </c>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="18"/>
+      <c r="F29" s="75"/>
+      <c r="G29" s="75"/>
+      <c r="H29" s="75"/>
+      <c r="I29" s="76"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
-      <c r="L29" s="19" t="s">
-        <v>53</v>
+      <c r="L29" s="138" t="s">
+        <v>68</v>
       </c>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
-      <c r="P29" s="17"/>
-      <c r="Q29" s="18"/>
+      <c r="M29" s="75"/>
+      <c r="N29" s="75"/>
+      <c r="O29" s="75"/>
+      <c r="P29" s="75"/>
+      <c r="Q29" s="76"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
@@ -3587,27 +3635,27 @@
       <c r="B30" s="11">
         <v>2027</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="128">
         <v>3</v>
       </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="28" t="s">
-        <v>59</v>
+      <c r="D30" s="118"/>
+      <c r="E30" s="117" t="s">
+        <v>52</v>
       </c>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="18"/>
+      <c r="F30" s="75"/>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
+      <c r="I30" s="76"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
-      <c r="L30" s="19" t="s">
-        <v>55</v>
+      <c r="L30" s="138" t="s">
+        <v>67</v>
       </c>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17"/>
-      <c r="O30" s="17"/>
-      <c r="P30" s="17"/>
-      <c r="Q30" s="18"/>
+      <c r="M30" s="75"/>
+      <c r="N30" s="75"/>
+      <c r="O30" s="75"/>
+      <c r="P30" s="75"/>
+      <c r="Q30" s="76"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
@@ -3621,26 +3669,26 @@
     </row>
     <row r="31" spans="1:27" ht="10.5" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="66" t="s">
+      <c r="B31" s="68"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="31"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="32"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="26"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
-      <c r="L31" s="67" t="s">
-        <v>54</v>
+      <c r="L31" s="121" t="s">
+        <v>62</v>
       </c>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
-      <c r="O31" s="31"/>
-      <c r="P31" s="31"/>
-      <c r="Q31" s="32"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="26"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
@@ -3654,22 +3702,22 @@
     </row>
     <row r="32" spans="1:27" ht="13.5" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="34"/>
+      <c r="B32" s="69"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="32"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
-      <c r="L32" s="68"/>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="34"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="32"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
@@ -3683,30 +3731,30 @@
     </row>
     <row r="33" spans="1:27" ht="17.25" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="22">
+      <c r="B33" s="68">
         <v>2023</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="116">
         <v>8</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="30" t="s">
+      <c r="D33" s="34"/>
+      <c r="E33" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="32"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="26"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
-      <c r="L33" s="67" t="s">
-        <v>56</v>
+      <c r="L33" s="121" t="s">
+        <v>49</v>
       </c>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
-      <c r="O33" s="31"/>
-      <c r="P33" s="31"/>
-      <c r="Q33" s="32"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="26"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
@@ -3720,22 +3768,22 @@
     </row>
     <row r="34" spans="1:27" ht="10.5" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="34"/>
+      <c r="B34" s="69"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="111"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="32"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="49"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="42"/>
+      <c r="L34" s="64"/>
+      <c r="M34" s="83"/>
+      <c r="N34" s="83"/>
+      <c r="O34" s="83"/>
+      <c r="P34" s="83"/>
+      <c r="Q34" s="84"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
@@ -3749,24 +3797,24 @@
     </row>
     <row r="35" spans="1:27" ht="12" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="30" t="s">
+      <c r="B35" s="68"/>
+      <c r="C35" s="116"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="32"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="26"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
-      <c r="L35" s="69"/>
-      <c r="M35" s="70"/>
-      <c r="N35" s="70"/>
-      <c r="O35" s="70"/>
-      <c r="P35" s="70"/>
-      <c r="Q35" s="70"/>
+      <c r="L35" s="122"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="28"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
@@ -3774,20 +3822,20 @@
     </row>
     <row r="36" spans="1:27" ht="12" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="34"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="111"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="32"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
-      <c r="L36" s="128" t="s">
+      <c r="L36" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="M36" s="129"/>
+      <c r="M36" s="62"/>
       <c r="N36" s="12" t="s">
         <v>35</v>
       </c>
@@ -3807,36 +3855,36 @@
     </row>
     <row r="37" spans="1:27" ht="10.5" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="22">
+      <c r="B37" s="68">
         <v>2025</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="116">
         <v>12</v>
       </c>
-      <c r="D37" s="25"/>
-      <c r="E37" s="30" t="s">
-        <v>51</v>
+      <c r="D37" s="34"/>
+      <c r="E37" s="87" t="s">
+        <v>48</v>
       </c>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="32"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="26"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
-      <c r="L37" s="100" t="s">
+      <c r="L37" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="M37" s="101"/>
-      <c r="N37" s="111" t="s">
+      <c r="M37" s="63"/>
+      <c r="N37" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="O37" s="113" t="s">
+      <c r="O37" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="P37" s="111" t="s">
+      <c r="P37" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="Q37" s="130" t="s">
+      <c r="Q37" s="66" t="s">
         <v>40</v>
       </c>
       <c r="R37" s="1"/>
@@ -3846,22 +3894,22 @@
     </row>
     <row r="38" spans="1:27" ht="13.5" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="34"/>
+      <c r="B38" s="69"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="111"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="32"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
-      <c r="L38" s="49"/>
-      <c r="M38" s="55"/>
-      <c r="N38" s="112"/>
-      <c r="O38" s="112"/>
-      <c r="P38" s="112"/>
-      <c r="Q38" s="131"/>
+      <c r="L38" s="64"/>
+      <c r="M38" s="65"/>
+      <c r="N38" s="22"/>
+      <c r="O38" s="22"/>
+      <c r="P38" s="22"/>
+      <c r="Q38" s="67"/>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
@@ -3875,20 +3923,20 @@
     </row>
     <row r="39" spans="1:27" ht="12.75" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="22">
+      <c r="B39" s="68">
         <v>2025</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="116">
         <v>12</v>
       </c>
-      <c r="D39" s="25"/>
-      <c r="E39" s="30" t="s">
+      <c r="D39" s="34"/>
+      <c r="E39" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="32"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="26"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="7"/>
@@ -3910,24 +3958,24 @@
     </row>
     <row r="40" spans="1:27" ht="10.5" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="34"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="111"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="32"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="M40" s="35"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="36"/>
-      <c r="P40" s="36"/>
-      <c r="Q40" s="37"/>
+      <c r="M40" s="141"/>
+      <c r="N40" s="41"/>
+      <c r="O40" s="41"/>
+      <c r="P40" s="41"/>
+      <c r="Q40" s="42"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
@@ -3942,25 +3990,25 @@
     <row r="41" spans="1:27" ht="24" customHeight="1">
       <c r="A41" s="1"/>
       <c r="B41" s="3"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="38" t="s">
+      <c r="C41" s="117"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="18"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="75"/>
+      <c r="H41" s="75"/>
+      <c r="I41" s="76"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
-      <c r="L41" s="39" t="s">
+      <c r="L41" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="18"/>
+      <c r="M41" s="75"/>
+      <c r="N41" s="75"/>
+      <c r="O41" s="75"/>
+      <c r="P41" s="75"/>
+      <c r="Q41" s="76"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
       <c r="T41" s="1"/>
@@ -3975,23 +4023,23 @@
     <row r="42" spans="1:27" ht="24" customHeight="1">
       <c r="A42" s="1"/>
       <c r="B42" s="3"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="18"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="88"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="75"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="76"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
-      <c r="L42" s="40" t="s">
+      <c r="L42" s="143" t="s">
         <v>46</v>
       </c>
-      <c r="M42" s="41"/>
-      <c r="N42" s="41"/>
-      <c r="O42" s="41"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="42"/>
+      <c r="M42" s="83"/>
+      <c r="N42" s="83"/>
+      <c r="O42" s="83"/>
+      <c r="P42" s="83"/>
+      <c r="Q42" s="84"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
       <c r="T42" s="1"/>
@@ -4006,15 +4054,15 @@
     <row r="43" spans="1:27" ht="24" customHeight="1">
       <c r="A43" s="1"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="63" t="s">
+      <c r="C43" s="139"/>
+      <c r="D43" s="140"/>
+      <c r="E43" s="119" t="s">
         <v>47</v>
       </c>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
-      <c r="I43" s="65"/>
+      <c r="F43" s="90"/>
+      <c r="G43" s="90"/>
+      <c r="H43" s="90"/>
+      <c r="I43" s="91"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -10587,6 +10635,86 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="L24:Q24"/>
+    <mergeCell ref="L25:Q25"/>
+    <mergeCell ref="L26:Q26"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E39:I40"/>
+    <mergeCell ref="M40:Q40"/>
+    <mergeCell ref="E41:I41"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="E42:I42"/>
+    <mergeCell ref="L42:Q42"/>
+    <mergeCell ref="L29:Q29"/>
+    <mergeCell ref="L30:Q30"/>
+    <mergeCell ref="L27:Q27"/>
+    <mergeCell ref="L28:Q28"/>
+    <mergeCell ref="E30:I30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="B15:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C20"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="D19:F20"/>
+    <mergeCell ref="E25:I25"/>
+    <mergeCell ref="E26:I26"/>
+    <mergeCell ref="E23:I23"/>
+    <mergeCell ref="E24:I24"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="E28:I28"/>
+    <mergeCell ref="E29:I29"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E43:I43"/>
+    <mergeCell ref="E31:I32"/>
+    <mergeCell ref="L31:Q32"/>
+    <mergeCell ref="E33:I34"/>
+    <mergeCell ref="L33:Q34"/>
+    <mergeCell ref="E35:I36"/>
+    <mergeCell ref="L35:Q35"/>
+    <mergeCell ref="E37:I38"/>
+    <mergeCell ref="B1:E4"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:Q3"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="L11:M12"/>
+    <mergeCell ref="N11:Q12"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="D5:E6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="B7:C9"/>
+    <mergeCell ref="D7:E9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="N16:Q16"/>
+    <mergeCell ref="L17:M18"/>
+    <mergeCell ref="N17:Q18"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="N4:Q5"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:Q7"/>
+    <mergeCell ref="N8:Q8"/>
+    <mergeCell ref="N9:Q9"/>
     <mergeCell ref="L20:M20"/>
     <mergeCell ref="N20:Q20"/>
     <mergeCell ref="N37:N38"/>
@@ -10611,86 +10739,6 @@
     <mergeCell ref="L23:Q23"/>
     <mergeCell ref="L13:M16"/>
     <mergeCell ref="N13:Q15"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="L17:M18"/>
-    <mergeCell ref="N17:Q18"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="N4:Q5"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:Q7"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="B1:E4"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="N2:Q3"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="L11:M12"/>
-    <mergeCell ref="N11:Q12"/>
-    <mergeCell ref="B5:C6"/>
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="B7:C9"/>
-    <mergeCell ref="D7:E9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E43:I43"/>
-    <mergeCell ref="E31:I32"/>
-    <mergeCell ref="L31:Q32"/>
-    <mergeCell ref="E33:I34"/>
-    <mergeCell ref="L33:Q34"/>
-    <mergeCell ref="E35:I36"/>
-    <mergeCell ref="L35:Q35"/>
-    <mergeCell ref="E37:I38"/>
-    <mergeCell ref="B15:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="D19:F20"/>
-    <mergeCell ref="E25:I25"/>
-    <mergeCell ref="E26:I26"/>
-    <mergeCell ref="E23:I23"/>
-    <mergeCell ref="E24:I24"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:I27"/>
-    <mergeCell ref="E28:I28"/>
-    <mergeCell ref="E29:I29"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="L24:Q24"/>
-    <mergeCell ref="L25:Q25"/>
-    <mergeCell ref="L26:Q26"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:D38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E39:I40"/>
-    <mergeCell ref="M40:Q40"/>
-    <mergeCell ref="E41:I41"/>
-    <mergeCell ref="L41:Q41"/>
-    <mergeCell ref="E42:I42"/>
-    <mergeCell ref="L42:Q42"/>
-    <mergeCell ref="L29:Q29"/>
-    <mergeCell ref="L30:Q30"/>
-    <mergeCell ref="L27:Q27"/>
-    <mergeCell ref="L28:Q28"/>
-    <mergeCell ref="E30:I30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D32"/>
   </mergeCells>
   <phoneticPr fontId="16"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
